--- a/artfynd/A 186-2023 artfynd.xlsx
+++ b/artfynd/A 186-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 186-2023 artfynd.xlsx
+++ b/artfynd/A 186-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96749199</v>
       </c>
       <c r="B2" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721995.064268294</v>
+        <v>721995</v>
       </c>
       <c r="R2" t="n">
-        <v>6397561.853067587</v>
+        <v>6397562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,12 +796,7 @@
         <v>96749198</v>
       </c>
       <c r="B3" t="n">
-        <v>89175</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721995.064268294</v>
+        <v>721995</v>
       </c>
       <c r="R3" t="n">
-        <v>6397561.853067587</v>
+        <v>6397562</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,19 +872,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -941,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106165877</v>
+        <v>96748439</v>
       </c>
       <c r="B4" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,49 +922,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västers, Västers myr, Gtl</t>
+          <t>NV om Västers myr, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721997.4303409236</v>
+        <v>722059</v>
       </c>
       <c r="R4" t="n">
-        <v>6397499.267119475</v>
+        <v>6397520</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,27 +971,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bäl</t>
+          <t>Boge</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,84 +995,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elina  Ambjörnsson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elina  Ambjörnsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Leif Andersson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106165860</v>
+        <v>96748441</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västers, Västers myr, Gtl</t>
+          <t>NV om Västers myr, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722013.5660130667</v>
+        <v>722059</v>
       </c>
       <c r="R5" t="n">
-        <v>6397518.379357624</v>
+        <v>6397520</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,27 +1077,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bäl</t>
+          <t>Boge</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,84 +1101,75 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elina  Ambjörnsson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elina  Ambjörnsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Leif Andersson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106165864</v>
+        <v>112363612</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>100515</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronspraktbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Buprestis haemorrhoidalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Herbst, 1780</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västers, Västers myr, Gtl</t>
+          <t>Västers myr, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>722013.5660130667</v>
+        <v>721946</v>
       </c>
       <c r="R6" t="n">
-        <v>6397518.379357624</v>
+        <v>6397557</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,22 +1193,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,22 +1212,671 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112363568</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5479</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105894</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smedbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ergates faber</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>721946</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6397557</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112363593</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>721933</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6397486</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106165864</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västers, Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>722014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6397518</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Elina  Ambjörnsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Elina  Ambjörnsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>106165860</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västers, Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>722014</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6397518</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106165877</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västers, Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721998</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6397499</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96748440</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NV om Västers myr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>722059</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6397520</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Boge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Leif Andersson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 186-2023 artfynd.xlsx
+++ b/artfynd/A 186-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96749199</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96749198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96748439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96748441</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363612</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363593</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165864</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165877</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,8 +1932,26 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96748440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>